--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,6 +1448,106 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>฿48,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A19 Pro หน้าจอ ProMotion 120Hz แบตเตอรี่อึดยิ่งขึ้น ระบบกล้องโปร เครื่องศูนย์แท้พร้อมประกันศูนย์ไทย</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>฿39,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) จอใหญ่เต็มตา แบตเตอรี่อึดทนทาน รองรับ Apple Intelligence เต็มรูปแบบ ชิป A18 เครื่องศูนย์ไทยแท้</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>฿34,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) พอร์ต USB-C กล้องหลัก 48MP หน้าจอ Dynamic Island คุ้มค่าที่สุดสำหรับรุ่นมาตรฐาน ใช้งานได้ยาวนาน</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>฿26,900.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G52"/>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1546,6 +1546,414 @@
       <c r="F56" t="inlineStr">
         <is>
           <t>฿26,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink ราคา 2250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ลด 35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet ราคา 4100.00 บาท</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBAKIWf</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ลด 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด ราคา 1319.00 บาท</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AOkJG7XeU</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ลด 39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 17/17 Air/17 Pro/17 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์ ราคา 690.00 บาท</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pltueeZSk</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-me464fn2gzy9c4.webp</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ลด 42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี ราคา 1798.00 บาท</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1AVOUsEit</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ลด 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rubber Killer - JOURNEY LOGO T-SHIRT (เสื้อยืดคอกลม) ราคา 950.00 บาท</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40ge9qm9Up</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lu0rwfi2o9ht0d.webp</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน ราคา 4730.00 บาท</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ ราคา 1955.00 บาท</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ลด 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix ราคา 9490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50ZBLhh7GG</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ลด 41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า ราคา 875.00 บาท</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ลด 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้ ราคา 634.00 บาท</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ลด 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 18 Pro/18 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์ ราคา 1250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAHHVDfOkK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-msm7y6m7hs7409.webp</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ลด 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2 ราคา 14290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ลด 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control ราคา 1287.00 บาท</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VcukpE2bD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ลด 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>🔥พร้อมส่ง🔥 เสื้อ Guns N' Roses Thailand Bankok (2017) Tee - Black (สีดำ) by XSHT ราคา 595.00 บาท</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBJt9y0</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-ly6pmx1kzfl554.webp</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ลด 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี ราคา 2107.00 บาท</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ลด 38%</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$G$52</definedName>
@@ -1473,6 +1473,11 @@
           <t>฿48,900.00</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>done 2026-09-19 21:51</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1563,7 +1568,6 @@
           <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
@@ -1589,7 +1593,6 @@
           <t>https://s.shopee.co.th/1VzJBAKIWf</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
@@ -1615,7 +1618,6 @@
           <t>https://s.shopee.co.th/9AOkJG7XeU</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
@@ -1641,7 +1643,6 @@
           <t>https://s.shopee.co.th/8pltueeZSk</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-me464fn2gzy9c4.webp</t>
@@ -1667,7 +1668,6 @@
           <t>https://s.shopee.co.th/1AVOUsEit</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
@@ -1693,13 +1693,11 @@
           <t>https://s.shopee.co.th/40ge9qm9Up</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lu0rwfi2o9ht0d.webp</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1715,13 +1713,11 @@
           <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1737,7 +1733,6 @@
           <t>https://s.shopee.co.th/4B04MAcB1P</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
@@ -1763,7 +1758,6 @@
           <t>https://s.shopee.co.th/50ZBLhh7GG</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
@@ -1789,7 +1783,6 @@
           <t>https://s.shopee.co.th/9KiAVfeVSA</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
@@ -1815,7 +1808,6 @@
           <t>https://s.shopee.co.th/5VVRwdnTF3</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
@@ -1841,7 +1833,6 @@
           <t>https://s.shopee.co.th/AAHHVDfOkK</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-msm7y6m7hs7409.webp</t>
@@ -1867,7 +1858,6 @@
           <t>https://s.shopee.co.th/9zxrIvShk4</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
@@ -1893,7 +1883,6 @@
           <t>https://s.shopee.co.th/4VcukpE2bD</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
@@ -1919,7 +1908,6 @@
           <t>https://s.shopee.co.th/1VzJBJt9y0</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-ly6pmx1kzfl554.webp</t>
@@ -1945,7 +1933,6 @@
           <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
@@ -1975,7 +1962,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "E"], "last_hooks": ["ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "เทียบข้อมูล"], "last_roles": ["R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1"], "recent_captions": ["ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การซื้อสมาร์ตโฟนราคาสูงผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าจะได้ iPhone 18 Pro Max เครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ไทย 1 ปีเต็ม ในราคา 48,900 บาท โดยไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงเรื่องบริการหลังการขายครับ เมื่อพิจารณาชิป A20 Pro กับราคา 48,900 บาทนี้แล้ว พี่คิดว่าตอบโจทย์สำหรับการตัดสินใจเปลี่ยนเครื่องใหม่ไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1603,6 +1603,11 @@
           <t>ลด 45%</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>done 2026-09-23 22:36</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1962,7 +1967,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "E"], "last_hooks": ["ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "เทียบข้อมูล"], "last_roles": ["R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1"], "recent_captions": ["ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การซื้อสมาร์ตโฟนราคาสูงผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าจะได้ iPhone 18 Pro Max เครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ไทย 1 ปีเต็ม ในราคา 48,900 บาท โดยไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงเรื่องบริการหลังการขายครับ เมื่อพิจารณาชิป A20 Pro กับราคา 48,900 บาทนี้แล้ว พี่คิดว่าตอบโจทย์สำหรับการตัดสินใจเปลี่ยนเครื่องใหม่ไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "E", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "เทียบข้อมูล", "คำถามเฉพาะ"], "last_roles": ["R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R1"], "recent_captions": ["เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การซื้อสมาร์ตโฟนราคาสูงผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าจะได้ iPhone 18 Pro Max เครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ไทย 1 ปีเต็ม ในราคา 48,900 บาท โดยไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงเรื่องบริการหลังการขายครับ เมื่อพิจารณาชิป A20 Pro กับราคา 48,900 บาทนี้แล้ว พี่คิดว่าตอบโจทย์สำหรับการตัดสินใจเปลี่ยนเครื่องใหม่ไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ในราคา 2,255 บาท ผมไปเจอกระเป๋าสะพายข้าง Pacsafe CX ที่ให้ระบบกันขโมยสำหรับการเดินทางและใช้งานประจำวัน พร้อมขนาดที่ใส่แท็บเล็ต 8 นิ้วได้ครับ ฟังก์ชันกันขโมยกับช่องใส่แท็บเล็ต 8 นิ้วในราคา 2,255 บาทนี้ คิดว่าเหมาะกับการสะพายเดินทางหรือเน้นใช้ในชีวิตประจำวันมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1503,6 +1503,11 @@
           <t>฿39,900.00</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>done 2026-09-26 22:08</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1967,7 +1972,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "E", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "เทียบข้อมูล", "คำถามเฉพาะ"], "last_roles": ["R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R1"], "recent_captions": ["เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การซื้อสมาร์ตโฟนราคาสูงผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าจะได้ iPhone 18 Pro Max เครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ไทย 1 ปีเต็ม ในราคา 48,900 บาท โดยไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงเรื่องบริการหลังการขายครับ เมื่อพิจารณาชิป A20 Pro กับราคา 48,900 บาทนี้แล้ว พี่คิดว่าตอบโจทย์สำหรับการตัดสินใจเปลี่ยนเครื่องใหม่ไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ในราคา 2,255 บาท ผมไปเจอกระเป๋าสะพายข้าง Pacsafe CX ที่ให้ระบบกันขโมยสำหรับการเดินทางและใช้งานประจำวัน พร้อมขนาดที่ใส่แท็บเล็ต 8 นิ้วได้ครับ ฟังก์ชันกันขโมยกับช่องใส่แท็บเล็ต 8 นิ้วในราคา 2,255 บาทนี้ คิดว่าเหมาะกับการสะพายเดินทางหรือเน้นใช้ในชีวิตประจำวันมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "E", "A", "C"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้"], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "เทียบข้อมูล", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ"], "last_roles": ["R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R1", "R2"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การซื้อสมาร์ตโฟนราคาสูงผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าจะได้ iPhone 18 Pro Max เครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ไทย 1 ปีเต็ม ในราคา 48,900 บาท โดยไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงเรื่องบริการหลังการขายครับ เมื่อพิจารณาชิป A20 Pro กับราคา 48,900 บาทนี้แล้ว พี่คิดว่าตอบโจทย์สำหรับการตัดสินใจเปลี่ยนเครื่องใหม่ไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ในราคา 2,255 บาท ผมไปเจอกระเป๋าสะพายข้าง Pacsafe CX ที่ให้ระบบกันขโมยสำหรับการเดินทางและใช้งานประจำวัน พร้อมขนาดที่ใส่แท็บเล็ต 8 นิ้วได้ครับ ฟังก์ชันกันขโมยกับช่องใส่แท็บเล็ต 8 นิ้วในราคา 2,255 บาทนี้ คิดว่าเหมาะกับการสะพายเดินทางหรือเน้นใช้ในชีวิตประจำวันมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ถ้าใครกังวลเรื่องซื้อสมาร์ทโฟนราคาสูงแล้วจะเจอเครื่องย้อมแมวหรือเครื่องหิ้ว ผมชี้เป้าร้านทางการใน Shopee Mall ที่วางจำหน่าย iPhone 17 Pro เครื่องศูนย์ไทยแท้ ประกันศูนย์ 1 ปีเต็ม พร้อมชิป A19 Pro และจอ ProMotion 120Hz ในราคา 39,900 บาทครับ ชิป A19 Pro คู่กับจอ ProMotion 120Hz ในงบ 39,900 บาทนี้ ตอบโจทย์การใช้งานของพี่ไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$G$52</definedName>
@@ -1638,6 +1638,11 @@
           <t>ลด 39%</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>done 2026-09-27T02:45:06.814842+00:00 live-graphics 17934053061405206</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1751,6 +1756,11 @@
       <c r="F64" t="inlineStr">
         <is>
           <t>ลด 30%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>done 2026-09-27T02:45:53.574601+00:00 live-graphics 111830598532037_1026107003782893</t>
         </is>
       </c>
     </row>
